--- a/docs/downloads/04/tbl_raisons_non_scol_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_raisons_non_scol_marovoay_tous.xlsx
@@ -423,12 +423,6 @@
           <t>Main-d'oeuvre exploitation</t>
         </is>
       </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>6.9</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -513,12 +507,6 @@
           <t>Besoin revenu</t>
         </is>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>6.7</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -549,12 +537,6 @@
           <t>Paresse</t>
         </is>
       </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -585,12 +567,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -603,12 +579,6 @@
           <t>Autre raison</t>
         </is>
       </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>15</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -639,12 +609,6 @@
           <t>Handicap / maladie</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>5</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -657,12 +621,6 @@
           <t>Trop jeune</t>
         </is>
       </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17">
-        <v>20</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -675,12 +633,6 @@
           <t>École trop éloignée</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -693,12 +645,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -729,12 +675,6 @@
           <t>Besoin revenu</t>
         </is>
       </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -765,12 +705,6 @@
           <t>Handicap / maladie</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -783,12 +717,6 @@
           <t>Main-d'oeuvre exploitation</t>
         </is>
       </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24">
-        <v>3.3</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -836,12 +764,6 @@
         <is>
           <t>École trop éloignée</t>
         </is>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_raisons_non_scol_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_raisons_non_scol_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
